--- a/output/yearly_surface_area_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_68_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497604405043</v>
+        <v>10.84497619165913</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907093780644</v>
+        <v>37.78907145214557</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.070325981807276</v>
+        <v>4.214642894331557</v>
       </c>
       <c r="C2" t="n">
-        <v>10.6814150222053</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="D2" t="n">
-        <v>21.69367902074177</v>
+        <v>24.53878386764903</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.72345024703866</v>
+        <v>13.74937659797658</v>
       </c>
       <c r="C3" t="n">
-        <v>24.87257808709294</v>
+        <v>26.72317250959818</v>
       </c>
       <c r="D3" t="n">
-        <v>80.04189032724246</v>
+        <v>70.61711236647307</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.01417074068274</v>
+        <v>29.26491731589317</v>
       </c>
       <c r="C4" t="n">
-        <v>72.65816584360218</v>
+        <v>73.61536985524283</v>
       </c>
       <c r="D4" t="n">
-        <v>109.8997832565007</v>
+        <v>76.4104055692335</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>38.06726723217008</v>
       </c>
       <c r="C5" t="n">
-        <v>132.8304643845935</v>
+        <v>121.5403657857552</v>
       </c>
       <c r="D5" t="n">
-        <v>76.72358308688824</v>
+        <v>55.39511421212629</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C6" t="n">
-        <v>153.0367956334013</v>
+        <v>138.425444551096</v>
       </c>
       <c r="D6" t="n">
-        <v>49.71079500453725</v>
+        <v>43.06927178530758</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.65521093382689</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="C7" t="n">
-        <v>125.282788034344</v>
+        <v>136.7211305365236</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>14.77039421039326</v>
       </c>
       <c r="C8" t="n">
-        <v>77.27336180126643</v>
+        <v>94.96445543179397</v>
       </c>
       <c r="D8" t="n">
         <v>35.9663271450819</v>
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
         <v>33.9468721174462</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.666124597358745</v>
+        <v>7.674451956020956</v>
       </c>
       <c r="C21" t="n">
-        <v>92.95176074297477</v>
+        <v>93.05272996675409</v>
       </c>
       <c r="D21" t="n">
-        <v>7.666124597358745</v>
+        <v>7.674451956020956</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.432590884674349</v>
+        <v>6.535494467171016</v>
       </c>
       <c r="C2" t="n">
-        <v>8.105309046261667</v>
+        <v>4.300054944601029</v>
       </c>
       <c r="D2" t="n">
-        <v>24.07932594206152</v>
+        <v>21.64851862634641</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.17505419099219</v>
+        <v>13.82300767579509</v>
       </c>
       <c r="C3" t="n">
-        <v>33.10944132572368</v>
+        <v>20.70996782108647</v>
       </c>
       <c r="D3" t="n">
-        <v>79.29576207201488</v>
+        <v>72.95367190258048</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.83174559414208</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="C4" t="n">
-        <v>67.38716241950105</v>
+        <v>69.42919764433444</v>
       </c>
       <c r="D4" t="n">
-        <v>120.5821800264102</v>
+        <v>91.57251711362125</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.77903431774902</v>
+        <v>40.96342295969817</v>
       </c>
       <c r="C5" t="n">
-        <v>131.897804065559</v>
+        <v>128.2407938672396</v>
       </c>
       <c r="D5" t="n">
-        <v>95.05772146369743</v>
+        <v>67.22517404830035</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.85543071223103</v>
+        <v>43.59254331167113</v>
       </c>
       <c r="C6" t="n">
-        <v>180.1664116925577</v>
+        <v>162.6166897314417</v>
       </c>
       <c r="D6" t="n">
-        <v>59.49194738194822</v>
+        <v>49.79129831628549</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.56024344842221</v>
+        <v>35.27321326588365</v>
       </c>
       <c r="C7" t="n">
-        <v>168.1616007650277</v>
+        <v>167.1435283957237</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.35868206941536</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C8" t="n">
-        <v>118.1631536831461</v>
+        <v>134.185276216454</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>65.00936947981526</v>
+        <v>81.98280553853837</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.840348731406892</v>
+        <v>7.852003565212923</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9444899168637</v>
+        <v>101.0945459021164</v>
       </c>
       <c r="D21" t="n">
-        <v>8.820392322832754</v>
+        <v>8.833504010864537</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.028511741152163</v>
+        <v>6.44811892149305</v>
       </c>
       <c r="C2" t="n">
-        <v>9.230391915328511</v>
+        <v>12.32486067911446</v>
       </c>
       <c r="D2" t="n">
-        <v>26.82920126165683</v>
+        <v>17.36711688812607</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.63156687346696</v>
+        <v>17.23458094805276</v>
       </c>
       <c r="C3" t="n">
-        <v>32.06388002070083</v>
+        <v>18.67284133477433</v>
       </c>
       <c r="D3" t="n">
-        <v>79.14849991637786</v>
+        <v>72.51679417419065</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.87454158250144</v>
+        <v>26.59750880345459</v>
       </c>
       <c r="C4" t="n">
-        <v>73.23248825058657</v>
+        <v>60.58463257677491</v>
       </c>
       <c r="D4" t="n">
-        <v>128.0738967575176</v>
+        <v>102.025184920737</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.8772090881737</v>
+        <v>40.76707341884881</v>
       </c>
       <c r="C5" t="n">
-        <v>126.9154344665064</v>
+        <v>127.7990074003286</v>
       </c>
       <c r="D5" t="n">
-        <v>111.8701508989241</v>
+        <v>80.84692344472485</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.24286120251001</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C6" t="n">
-        <v>193.1274448840241</v>
+        <v>178.7978553928376</v>
       </c>
       <c r="D6" t="n">
-        <v>71.08442427369457</v>
+        <v>56.75483478250812</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.32743037379547</v>
+        <v>42.16017341117502</v>
       </c>
       <c r="C7" t="n">
-        <v>205.5907319894373</v>
+        <v>195.4698949063569</v>
       </c>
       <c r="D7" t="n">
-        <v>49.52622643613884</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.70077223884975</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="C8" t="n">
-        <v>161.3060565462722</v>
+        <v>172.8219571170873</v>
       </c>
       <c r="D8" t="n">
         <v>39.97185777840888</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>15.53124868118453</v>
       </c>
       <c r="C9" t="n">
-        <v>99.17811657842124</v>
+        <v>117.0390525617834</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>54.09429850399926</v>
+        <v>66.33669237595699</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>41.40324593120072</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.998924363199099</v>
+        <v>8.014669647777284</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9854789031878</v>
+        <v>109.1998739509655</v>
       </c>
       <c r="D21" t="n">
-        <v>9.998655453998873</v>
+        <v>10.0183370597216</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.655447613538375</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C2" t="n">
-        <v>6.34994415106837</v>
+        <v>8.380198403450773</v>
       </c>
       <c r="D2" t="n">
-        <v>22.2228410333308</v>
+        <v>14.58975263281185</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.62589737141974</v>
+        <v>19.58095796120263</v>
       </c>
       <c r="C3" t="n">
-        <v>47.8454743664683</v>
+        <v>34.93549205562275</v>
       </c>
       <c r="D3" t="n">
-        <v>87.31173207719009</v>
+        <v>78.18638716621598</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.67185958707009</v>
+        <v>19.57801271808989</v>
       </c>
       <c r="C4" t="n">
-        <v>102.7143718091183</v>
+        <v>96.94562229896403</v>
       </c>
       <c r="D4" t="n">
-        <v>123.811148225678</v>
+        <v>95.65658756328797</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.19441140763665</v>
       </c>
       <c r="C5" t="n">
-        <v>115.4044426342126</v>
+        <v>106.8386939146592</v>
       </c>
       <c r="D5" t="n">
-        <v>72.52661165123313</v>
+        <v>55.64055113818799</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.78872862160447</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="C6" t="n">
-        <v>135.4065703605371</v>
+        <v>128.7247954854333</v>
       </c>
       <c r="D6" t="n">
-        <v>32.60384125803657</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>113.425239262451</v>
+        <v>121.5099316069235</v>
       </c>
       <c r="D7" t="n">
         <v>28.086820070797</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>73.1009340582175</v>
+        <v>86.20235717139117</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>41.26874649571891</v>
+        <v>50.58749570442963</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.829396883639308</v>
+        <v>3.654064955206628</v>
       </c>
       <c r="C2" t="n">
-        <v>2.91480893390878</v>
+        <v>4.646611884200153</v>
       </c>
       <c r="D2" t="n">
-        <v>15.87584212537517</v>
+        <v>10.36823750455056</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.93514789825748</v>
+        <v>20.49398332615217</v>
       </c>
       <c r="C3" t="n">
-        <v>37.29659528433633</v>
+        <v>34.53297549688155</v>
       </c>
       <c r="D3" t="n">
-        <v>86.35452806554945</v>
+        <v>72.96839811814418</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.23640557474101</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="C4" t="n">
-        <v>113.3074295379414</v>
+        <v>94.90358707413067</v>
       </c>
       <c r="D4" t="n">
-        <v>136.0888850149886</v>
+        <v>111.1122416712455</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.80800372279091</v>
+        <v>29.86967390170921</v>
       </c>
       <c r="C5" t="n">
-        <v>151.655476613526</v>
+        <v>142.5988540418492</v>
       </c>
       <c r="D5" t="n">
-        <v>93.06968236259763</v>
+        <v>71.02944640225674</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>160.4431003142393</v>
+        <v>152.6342790746601</v>
       </c>
       <c r="D6" t="n">
-        <v>40.6139207769863</v>
+        <v>36.50825187782615</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.33097214951819</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>146.6623077897268</v>
+        <v>149.4769784578023</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>96.63342652901355</v>
+        <v>113.0727918366264</v>
       </c>
       <c r="D8" t="n">
         <v>27.95526587842792</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>55.91249525226433</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.596722677732814</v>
+        <v>2.991385254840031</v>
       </c>
       <c r="C2" t="n">
-        <v>11.58167766699962</v>
+        <v>10.58127675637212</v>
       </c>
       <c r="D2" t="n">
-        <v>12.31406145436774</v>
+        <v>13.44798005277281</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.26341148437441</v>
+        <v>16.40991287648544</v>
       </c>
       <c r="C3" t="n">
-        <v>23.84665173615502</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D3" t="n">
-        <v>79.60010386033139</v>
+        <v>65.60529033629311</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.18008610270045</v>
+        <v>33.22136056400782</v>
       </c>
       <c r="C4" t="n">
-        <v>103.0972534137745</v>
+        <v>90.42387229965247</v>
       </c>
       <c r="D4" t="n">
-        <v>146.3756374600867</v>
+        <v>120.5566545860998</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.78408192499049</v>
+        <v>35.07293673421731</v>
       </c>
       <c r="C5" t="n">
-        <v>179.0216938694059</v>
+        <v>158.4049920802229</v>
       </c>
       <c r="D5" t="n">
-        <v>116.1407534123977</v>
+        <v>90.76257525761763</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.4428346345401</v>
+        <v>35.34095385747668</v>
       </c>
       <c r="C6" t="n">
-        <v>199.4469548562608</v>
+        <v>189.2632859201086</v>
       </c>
       <c r="D6" t="n">
-        <v>56.19131160027045</v>
+        <v>47.53720558733482</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>185.3490578232766</v>
+        <v>184.3309854539726</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>140.7777120504714</v>
+        <v>152.3770611761474</v>
       </c>
       <c r="D8" t="n">
         <v>29.54078842078653</v>
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>77.87811838708245</v>
+        <v>91.52342972840887</v>
       </c>
       <c r="D9" t="n">
         <v>29.17656002251095</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.555088363526948</v>
+        <v>1.785799074024948</v>
       </c>
       <c r="C2" t="n">
-        <v>5.503677630007619</v>
+        <v>4.962734644967626</v>
       </c>
       <c r="D2" t="n">
-        <v>8.62465358180823</v>
+        <v>9.414960483726912</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.73817646260236</v>
+        <v>15.49197877301467</v>
       </c>
       <c r="C3" t="n">
-        <v>34.33171721751096</v>
+        <v>34.18936380039517</v>
       </c>
       <c r="D3" t="n">
-        <v>75.93818492349078</v>
+        <v>64.30447462816608</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.02617269731195</v>
+        <v>36.75663404700058</v>
       </c>
       <c r="C4" t="n">
-        <v>97.82624998967341</v>
+        <v>89.68363453065037</v>
       </c>
       <c r="D4" t="n">
-        <v>154.7607446020587</v>
+        <v>127.4485234699124</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.60031517784709</v>
+        <v>37.06097583531709</v>
       </c>
       <c r="C5" t="n">
-        <v>210.3885330200915</v>
+        <v>185.3048791765855</v>
       </c>
       <c r="D5" t="n">
-        <v>122.1785017935156</v>
+        <v>96.03946916794425</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.88810612391165</v>
+        <v>30.3497485290859</v>
       </c>
       <c r="C6" t="n">
-        <v>238.0885444954152</v>
+        <v>229.9979616647173</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66174867705392</v>
+        <v>46.97368240509714</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.246279805045708</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>190.9783991594278</v>
+        <v>196.7275137154971</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>98.71964040053801</v>
+        <v>113.7403802755142</v>
       </c>
       <c r="D8" t="n">
         <v>31.2097595180061</v>
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.121556788877357</v>
+        <v>2.052834449580081</v>
       </c>
       <c r="C2" t="n">
-        <v>7.094108910887452</v>
+        <v>4.516039439535327</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6333093846972</v>
+        <v>10.67257929286708</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.213702204356315</v>
+        <v>10.84340339340602</v>
       </c>
       <c r="C3" t="n">
-        <v>27.92090470877929</v>
+        <v>26.53173170727005</v>
       </c>
       <c r="D3" t="n">
-        <v>67.09754684674826</v>
+        <v>57.63840771633024</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.89930625928586</v>
+        <v>33.75739481052658</v>
       </c>
       <c r="C4" t="n">
-        <v>91.84053423688061</v>
+        <v>88.29249803373266</v>
       </c>
       <c r="D4" t="n">
-        <v>156.6113390245639</v>
+        <v>130.052118381575</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.19627709205391</v>
+        <v>44.96404485450392</v>
       </c>
       <c r="C5" t="n">
-        <v>198.1903177948249</v>
+        <v>177.4263538500048</v>
       </c>
       <c r="D5" t="n">
-        <v>143.7033202091269</v>
+        <v>116.9261515757951</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.13340418125311</v>
+        <v>38.44033135978387</v>
       </c>
       <c r="C6" t="n">
-        <v>282.4056176128205</v>
+        <v>261.313749934782</v>
       </c>
       <c r="D6" t="n">
-        <v>73.49952362614172</v>
+        <v>61.18251692866124</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.85187926984575</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>258.5903818032014</v>
+        <v>258.9497014629557</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>159.6370854490526</v>
+        <v>174.0736854400019</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>63.6781195928566</v>
+        <v>74.54999366968578</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.446114368355552</v>
+        <v>1.495201753567892</v>
       </c>
       <c r="C2" t="n">
-        <v>3.979023445312322</v>
+        <v>3.442989198793564</v>
       </c>
       <c r="D2" t="n">
-        <v>8.59029241215959</v>
+        <v>7.972773106188347</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.457756472086272</v>
+        <v>9.336420667387166</v>
       </c>
       <c r="C3" t="n">
-        <v>28.29887757491431</v>
+        <v>22.64401079845268</v>
       </c>
       <c r="D3" t="n">
-        <v>62.41951903601221</v>
+        <v>53.9863062565321</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.45337181737955</v>
+        <v>29.34149363682442</v>
       </c>
       <c r="C4" t="n">
-        <v>84.10632582282423</v>
+        <v>81.01774754526377</v>
       </c>
       <c r="D4" t="n">
-        <v>155.577558691992</v>
+        <v>130.0010675009542</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.92062697133881</v>
+        <v>48.866491978885</v>
       </c>
       <c r="C5" t="n">
-        <v>193.9933463591698</v>
+        <v>177.745421853885</v>
       </c>
       <c r="D5" t="n">
-        <v>157.3250696055514</v>
+        <v>130.9406000539184</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.48687441251096</v>
+        <v>44.88059629964295</v>
       </c>
       <c r="C6" t="n">
-        <v>307.0396310077815</v>
+        <v>281.4395778718417</v>
       </c>
       <c r="D6" t="n">
-        <v>88.7549012024329</v>
+        <v>72.89574878802993</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.35471402086936</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>314.2250424551638</v>
+        <v>308.4160412891355</v>
       </c>
       <c r="D7" t="n">
-        <v>45.15450390912779</v>
+        <v>43.17824578047897</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>205.45034206773</v>
+        <v>220.8048761621501</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>72.88593131098743</v>
+        <v>86.97499261463339</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.567270246605409</v>
+        <v>2.307107104980004</v>
       </c>
       <c r="C2" t="n">
-        <v>11.4805576534622</v>
+        <v>9.371763584740052</v>
       </c>
       <c r="D2" t="n">
-        <v>12.20508745919635</v>
+        <v>7.702792487520473</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.764241682260523</v>
+        <v>7.299294181075036</v>
       </c>
       <c r="C3" t="n">
-        <v>22.48693116577319</v>
+        <v>18.36849954645782</v>
       </c>
       <c r="D3" t="n">
-        <v>56.08724634362028</v>
+        <v>48.83213080923635</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.50969128942011</v>
+        <v>23.94286301117121</v>
       </c>
       <c r="C4" t="n">
-        <v>78.00574558863457</v>
+        <v>69.19946868154068</v>
       </c>
       <c r="D4" t="n">
-        <v>151.8125562462055</v>
+        <v>127.5378625109989</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.32528695193774</v>
+        <v>47.49204519293946</v>
       </c>
       <c r="C5" t="n">
-        <v>177.2545480017616</v>
+        <v>164.9827016986765</v>
       </c>
       <c r="D5" t="n">
-        <v>171.5849550097363</v>
+        <v>142.9424657383356</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>52.36740429222912</v>
       </c>
       <c r="C6" t="n">
-        <v>308.6496972427463</v>
+        <v>285.7062533944983</v>
       </c>
       <c r="D6" t="n">
-        <v>108.719722515996</v>
+        <v>88.91590782592939</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>29.16477905005999</v>
       </c>
       <c r="C7" t="n">
-        <v>365.7874136299105</v>
+        <v>349.3185958911703</v>
       </c>
       <c r="D7" t="n">
-        <v>54.85613472249477</v>
+        <v>51.02339168511523</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>287.0630287217674</v>
+        <v>294.4065015495335</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>135.565613488625</v>
+        <v>156.5327992082241</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>57.36842709766236</v>
       </c>
       <c r="D10" t="n">
         <v>26.33538216642069</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3739,7 +3739,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.382521751757761</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="C2" t="n">
-        <v>6.596362824834318</v>
+        <v>11.21254053020282</v>
       </c>
       <c r="D2" t="n">
-        <v>9.285369786766333</v>
+        <v>11.65629049252238</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.852557917913731</v>
+        <v>1.650317890838888</v>
       </c>
       <c r="C2" t="n">
-        <v>6.705336820005715</v>
+        <v>5.323036052426207</v>
       </c>
       <c r="D2" t="n">
-        <v>9.08018451657875</v>
+        <v>5.668611244321084</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.410051745205678</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C3" t="n">
-        <v>32.03933632809466</v>
+        <v>26.56118413839745</v>
       </c>
       <c r="D3" t="n">
-        <v>61.18251692866122</v>
+        <v>52.63640316319274</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.63503620039422</v>
+        <v>34.98261594542659</v>
       </c>
       <c r="C4" t="n">
-        <v>110.0146477378976</v>
+        <v>97.82624998967341</v>
       </c>
       <c r="D4" t="n">
-        <v>156.9431697485993</v>
+        <v>131.6985092815969</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.48264432205772</v>
+        <v>30.80233422074368</v>
       </c>
       <c r="C5" t="n">
-        <v>261.6848505669873</v>
+        <v>244.2588288166065</v>
       </c>
       <c r="D5" t="n">
-        <v>156.6623899051848</v>
+        <v>129.4679784975481</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>298.3855249948459</v>
+        <v>286.0685182973654</v>
       </c>
       <c r="D6" t="n">
-        <v>83.64294090641977</v>
+        <v>72.77499382040757</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>201.8777621719759</v>
+        <v>207.0280106284546</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>32.15910954801276</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>99.88792016859172</v>
+        <v>115.3259028178728</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.78422079371073</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>43.70937128847648</v>
       </c>
       <c r="D9" t="n">
         <v>20.07968579496001</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.735370088209866</v>
+        <v>6.446155426084557</v>
       </c>
       <c r="C2" t="n">
-        <v>7.540804116319751</v>
+        <v>7.149086782325274</v>
       </c>
       <c r="D2" t="n">
-        <v>26.38545129933727</v>
+        <v>11.62094757516949</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.316785713302229</v>
+        <v>12.36511233498858</v>
       </c>
       <c r="C3" t="n">
-        <v>16.6209886328985</v>
+        <v>28.2546989282232</v>
       </c>
       <c r="D3" t="n">
-        <v>10.93666942530947</v>
+        <v>12.92470852640926</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39852337509886</v>
+        <v>13.39707765108028</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14521061081169</v>
+        <v>70.13764182036144</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576296867658689</v>
+        <v>1.576126782480032</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.984913931537803</v>
+        <v>3.85041449605599</v>
       </c>
       <c r="C2" t="n">
-        <v>9.651561680450394</v>
+        <v>5.595961914206819</v>
       </c>
       <c r="D2" t="n">
-        <v>19.48867367700343</v>
+        <v>13.62567638724148</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.58524480491811</v>
+        <v>18.30959468420301</v>
       </c>
       <c r="C3" t="n">
-        <v>24.62223242251001</v>
+        <v>28.01907947920397</v>
       </c>
       <c r="D3" t="n">
-        <v>30.45381378573606</v>
+        <v>19.5613230071177</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.96317661332413</v>
+        <v>14.39634833507523</v>
       </c>
       <c r="C4" t="n">
-        <v>25.8700337546077</v>
+        <v>43.59745205019236</v>
       </c>
       <c r="D4" t="n">
-        <v>20.80323385298991</v>
+        <v>21.8370141855618</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44023945883177</v>
+        <v>15.43822450806219</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14028329664043</v>
+        <v>86.12904199234694</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250576728175111</v>
+        <v>3.250152528013092</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.671155576806324</v>
+        <v>4.3245986372072</v>
       </c>
       <c r="C2" t="n">
-        <v>6.950773746067417</v>
+        <v>6.960591223109885</v>
       </c>
       <c r="D2" t="n">
-        <v>27.58711048933537</v>
+        <v>13.21628759457056</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.57895340806514</v>
+        <v>15.50179625005713</v>
       </c>
       <c r="C3" t="n">
-        <v>32.46639657944202</v>
+        <v>24.23444207933251</v>
       </c>
       <c r="D3" t="n">
-        <v>38.97538385859838</v>
+        <v>25.92304813063703</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.86253962587222</v>
+        <v>26.36777984066083</v>
       </c>
       <c r="C4" t="n">
-        <v>46.92852201070178</v>
+        <v>59.25730968063323</v>
       </c>
       <c r="D4" t="n">
-        <v>31.37076614150258</v>
+        <v>26.73789872516188</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.940195505498956</v>
+        <v>12.61545799957152</v>
       </c>
       <c r="C5" t="n">
-        <v>29.52606220522283</v>
+        <v>48.25289966373074</v>
       </c>
       <c r="D5" t="n">
-        <v>30.13965452037709</v>
+        <v>30.50780990946964</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.23368131580652</v>
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73249150755391</v>
+        <v>16.72905551818743</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0681981960788</v>
+        <v>102.0472386609433</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183122876888477</v>
+        <v>4.182263879546857</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.724169952835651</v>
+        <v>4.590652265058085</v>
       </c>
       <c r="C2" t="n">
-        <v>11.05349740211484</v>
+        <v>6.758351196035043</v>
       </c>
       <c r="D2" t="n">
-        <v>32.7785923493925</v>
+        <v>17.62924352515997</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.30053797068654</v>
+        <v>15.26126806251667</v>
       </c>
       <c r="C3" t="n">
-        <v>29.28062527916112</v>
+        <v>25.82487336021235</v>
       </c>
       <c r="D3" t="n">
-        <v>51.27177385428967</v>
+        <v>30.19855938263188</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.09150782513998</v>
+        <v>28.14179794223482</v>
       </c>
       <c r="C4" t="n">
-        <v>66.098127683825</v>
+        <v>60.03583561010095</v>
       </c>
       <c r="D4" t="n">
-        <v>43.17628228507048</v>
+        <v>33.3362250454047</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.35301256736813</v>
+        <v>25.96722677732814</v>
       </c>
       <c r="C5" t="n">
-        <v>60.37748381117885</v>
+        <v>81.28870991163591</v>
       </c>
       <c r="D5" t="n">
-        <v>34.14027641518284</v>
+        <v>32.88854809226815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.660397409788615</v>
+        <v>11.59247689174634</v>
       </c>
       <c r="C6" t="n">
-        <v>30.02773528209295</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05474616220388</v>
+        <v>18.05148078474255</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7857249629491</v>
+        <v>117.7644222623681</v>
       </c>
       <c r="D21" t="n">
-        <v>6.018248720734627</v>
+        <v>6.017160261580849</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.522911673465055</v>
+        <v>5.177737392197677</v>
       </c>
       <c r="C2" t="n">
-        <v>8.373326169521047</v>
+        <v>11.39907259400971</v>
       </c>
       <c r="D2" t="n">
-        <v>34.03817465394116</v>
+        <v>29.54766065471625</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.05862712481433</v>
+        <v>13.81319019875262</v>
       </c>
       <c r="C3" t="n">
-        <v>34.67532891399734</v>
+        <v>24.48969648243668</v>
       </c>
       <c r="D3" t="n">
-        <v>60.94198874112075</v>
+        <v>34.69496386808228</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.12680968476386</v>
+        <v>21.07125097624929</v>
       </c>
       <c r="C4" t="n">
-        <v>58.019325825578</v>
+        <v>52.37820351697583</v>
       </c>
       <c r="D4" t="n">
-        <v>50.87220253866122</v>
+        <v>35.35273482992764</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.96598298771663</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="C5" t="n">
-        <v>69.43410638285567</v>
+        <v>72.20754364735292</v>
       </c>
       <c r="D5" t="n">
-        <v>33.37942194439156</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.54593383901924</v>
+        <v>12.71952325622168</v>
       </c>
       <c r="C6" t="n">
-        <v>42.94851681768522</v>
+        <v>59.49194738194822</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>27.90716024091983</v>
       </c>
       <c r="D7" t="n">
         <v>30.78171751895449</v>
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053835976839632</v>
+        <v>7.053763038088216</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12971228287155</v>
+        <v>66.12902848207702</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40864748552477</v>
+        <v>4.408601898805135</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.339324852770901</v>
+        <v>4.042837046088365</v>
       </c>
       <c r="C2" t="n">
-        <v>5.540984042768997</v>
+        <v>5.521349088684061</v>
       </c>
       <c r="D2" t="n">
-        <v>28.78778793162922</v>
+        <v>31.03991716517141</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15327581504952</v>
+        <v>16.6209886328985</v>
       </c>
       <c r="C3" t="n">
-        <v>33.41378311404019</v>
+        <v>37.42422248588841</v>
       </c>
       <c r="D3" t="n">
-        <v>74.80917506360696</v>
+        <v>51.12942043717388</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.75967710110456</v>
+        <v>24.69586350032851</v>
       </c>
       <c r="C4" t="n">
-        <v>75.93818492349079</v>
+        <v>58.10866486666446</v>
       </c>
       <c r="D4" t="n">
-        <v>71.01177494358029</v>
+        <v>44.98858854711009</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.93639168786899</v>
+        <v>27.39076094848602</v>
       </c>
       <c r="C5" t="n">
-        <v>91.57251711362125</v>
+        <v>87.4000893705723</v>
       </c>
       <c r="D5" t="n">
-        <v>44.39953992456201</v>
+        <v>36.69282044622454</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.47551004622073</v>
+        <v>21.53463589265379</v>
       </c>
       <c r="C6" t="n">
-        <v>82.55614619781855</v>
+        <v>92.13604029585892</v>
       </c>
       <c r="D6" t="n">
-        <v>35.30070220160257</v>
+        <v>34.17365583712723</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>44.85507085933252</v>
+        <v>61.74309486778615</v>
       </c>
       <c r="D7" t="n">
         <v>33.0574086973986</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>24.28352946454485</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>33.59540643932586</v>
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272059583799836</v>
+        <v>7.274599265480937</v>
       </c>
       <c r="C21" t="n">
-        <v>75.4476181819233</v>
+        <v>75.47396737936474</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454044687849876</v>
+        <v>5.455949449110703</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.153373626040755</v>
+        <v>3.698243601897735</v>
       </c>
       <c r="C2" t="n">
-        <v>6.130032665317084</v>
+        <v>6.669012154948583</v>
       </c>
       <c r="D2" t="n">
-        <v>23.1790632972672</v>
+        <v>28.00435326364027</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.04037482906113</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C3" t="n">
-        <v>26.32556468937822</v>
+        <v>27.89636101617312</v>
       </c>
       <c r="D3" t="n">
-        <v>80.48367679415351</v>
+        <v>64.09830761027426</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.50366193447439</v>
+        <v>29.18834099496192</v>
       </c>
       <c r="C4" t="n">
-        <v>80.44342513827939</v>
+        <v>78.15889823049707</v>
       </c>
       <c r="D4" t="n">
-        <v>92.55524656557229</v>
+        <v>60.49529353568845</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>32.66765485881262</v>
       </c>
       <c r="C5" t="n">
-        <v>118.9387343695011</v>
+        <v>98.88653751026</v>
       </c>
       <c r="D5" t="n">
-        <v>59.8375225738431</v>
+        <v>44.30136515413732</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.52584122104457</v>
+        <v>30.22899356146354</v>
       </c>
       <c r="C6" t="n">
-        <v>116.6492987231975</v>
+        <v>118.0983583346658</v>
       </c>
       <c r="D6" t="n">
-        <v>40.93593402397926</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>84.08080038251383</v>
+        <v>100.7891645610903</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>43.30979997284804</v>
+        <v>57.24570863463151</v>
       </c>
       <c r="D8" t="n">
         <v>33.79666471869644</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.5124976638126</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
         <v>32.9484347022272</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.476455320495192</v>
+        <v>7.48192327383124</v>
       </c>
       <c r="C21" t="n">
-        <v>84.11012235557091</v>
+        <v>84.17163683060144</v>
       </c>
       <c r="D21" t="n">
-        <v>6.541898405433293</v>
+        <v>6.546682864602334</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_68_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619165913</v>
+        <v>10.84497613040416</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907145214557</v>
+        <v>37.78907123870403</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.214642894331557</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C2" t="n">
-        <v>3.892629647338603</v>
+        <v>4.895975801078843</v>
       </c>
       <c r="D2" t="n">
-        <v>24.53878386764903</v>
+        <v>22.70487915611599</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.74937659797658</v>
+        <v>15.87486037767093</v>
       </c>
       <c r="C3" t="n">
-        <v>26.72317250959818</v>
+        <v>14.13716694115407</v>
       </c>
       <c r="D3" t="n">
-        <v>70.61711236647307</v>
+        <v>58.34526606338795</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.26491731589317</v>
+        <v>33.69358120975053</v>
       </c>
       <c r="C4" t="n">
-        <v>73.61536985524283</v>
+        <v>39.71758512300897</v>
       </c>
       <c r="D4" t="n">
-        <v>76.4104055692335</v>
+        <v>74.7767773893668</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.06726723217008</v>
+        <v>42.58330667170541</v>
       </c>
       <c r="C5" t="n">
-        <v>121.5403657857552</v>
+        <v>78.39255418410782</v>
       </c>
       <c r="D5" t="n">
-        <v>55.39511421212629</v>
+        <v>60.30385273336034</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>39.64788103600744</v>
       </c>
       <c r="C6" t="n">
-        <v>138.425444551096</v>
+        <v>112.7851397592821</v>
       </c>
       <c r="D6" t="n">
-        <v>43.06927178530758</v>
+        <v>44.1560664939088</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.66761380108361</v>
+        <v>28.56591295046944</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7211305365236</v>
+        <v>96.41744203407924</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>94.96445543179397</v>
+        <v>56.24432597629976</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.674451956020956</v>
+        <v>7.723035795686934</v>
       </c>
       <c r="C21" t="n">
-        <v>93.05272996675409</v>
+        <v>96.53794744608668</v>
       </c>
       <c r="D21" t="n">
-        <v>7.674451956020956</v>
+        <v>8.6884152701478</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.535494467171016</v>
+        <v>7.10687163104266</v>
       </c>
       <c r="C2" t="n">
-        <v>4.300054944601029</v>
+        <v>6.90070461315083</v>
       </c>
       <c r="D2" t="n">
-        <v>21.64851862634641</v>
+        <v>19.93536888243573</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.82300767579509</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="C3" t="n">
-        <v>20.70996782108647</v>
+        <v>16.75352457297182</v>
       </c>
       <c r="D3" t="n">
-        <v>72.95367190258048</v>
+        <v>62.27225688037518</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.43984833369835</v>
+        <v>31.83022406709009</v>
       </c>
       <c r="C4" t="n">
-        <v>69.42919764433444</v>
+        <v>37.3820073346058</v>
       </c>
       <c r="D4" t="n">
-        <v>91.57251711362125</v>
+        <v>85.79100488331179</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.96342295969817</v>
+        <v>46.95208395560371</v>
       </c>
       <c r="C5" t="n">
-        <v>128.2407938672396</v>
+        <v>75.00552460445633</v>
       </c>
       <c r="D5" t="n">
-        <v>67.22517404830035</v>
+        <v>71.49577656177398</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.59254331167113</v>
+        <v>48.42274201656544</v>
       </c>
       <c r="C6" t="n">
-        <v>162.6166897314417</v>
+        <v>119.1851530432671</v>
       </c>
       <c r="D6" t="n">
-        <v>49.79129831628549</v>
+        <v>52.48815925985148</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.27321326588365</v>
+        <v>37.84833749412304</v>
       </c>
       <c r="C7" t="n">
-        <v>167.1435283957237</v>
+        <v>128.9957578518054</v>
       </c>
       <c r="D7" t="n">
-        <v>41.86074036137975</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.61317570899353</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="C8" t="n">
-        <v>134.185276216454</v>
+        <v>92.12720456652069</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>11.53749902030851</v>
       </c>
       <c r="C9" t="n">
-        <v>81.98280553853837</v>
+        <v>51.80780810080841</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.852003565212923</v>
+        <v>7.916685815547335</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0945459021164</v>
+        <v>105.8856727829456</v>
       </c>
       <c r="D21" t="n">
-        <v>8.833504010864537</v>
+        <v>9.895857269434169</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.44811892149305</v>
+        <v>7.63308840051895</v>
       </c>
       <c r="C2" t="n">
-        <v>12.32486067911446</v>
+        <v>5.592034923389832</v>
       </c>
       <c r="D2" t="n">
-        <v>17.36711688812607</v>
+        <v>17.86388122647496</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23458094805276</v>
+        <v>19.32570355809846</v>
       </c>
       <c r="C3" t="n">
-        <v>18.67284133477433</v>
+        <v>21.72607669498191</v>
       </c>
       <c r="D3" t="n">
-        <v>72.51679417419065</v>
+        <v>63.17055602976101</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.59750880345459</v>
+        <v>30.13278228644735</v>
       </c>
       <c r="C4" t="n">
-        <v>60.58463257677491</v>
+        <v>39.14326271602458</v>
       </c>
       <c r="D4" t="n">
-        <v>102.025184920737</v>
+        <v>95.59277396251193</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.76707341884881</v>
+        <v>47.73748211900116</v>
       </c>
       <c r="C5" t="n">
-        <v>127.7990074003286</v>
+        <v>71.98665041389738</v>
       </c>
       <c r="D5" t="n">
-        <v>80.84692344472485</v>
+        <v>82.98222470146166</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.30198704894308</v>
+        <v>55.18502020341747</v>
       </c>
       <c r="C6" t="n">
-        <v>178.7978553928376</v>
+        <v>118.5411265492811</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>61.70578845502478</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.16017341117502</v>
+        <v>47.01098881785852</v>
       </c>
       <c r="C7" t="n">
-        <v>195.4698949063569</v>
+        <v>150.2555043872701</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>47.19064864773568</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.53940576245478</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>172.8219571170873</v>
+        <v>128.0935317116026</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.53124868118453</v>
+        <v>16.86249856814321</v>
       </c>
       <c r="C9" t="n">
-        <v>117.0390525617834</v>
+        <v>80.87343063273947</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>66.33669237595699</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>37.43894870145212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>41.40324593120072</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>36.45032876327558</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.014669647777284</v>
+        <v>8.097085629343317</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1998739509655</v>
+        <v>114.3713345144744</v>
       </c>
       <c r="D21" t="n">
-        <v>10.0183370597216</v>
+        <v>11.13349274034706</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.928774385946488</v>
+        <v>6.840818003191774</v>
       </c>
       <c r="C2" t="n">
-        <v>8.380198403450773</v>
+        <v>3.623630776374977</v>
       </c>
       <c r="D2" t="n">
-        <v>14.58975263281185</v>
+        <v>14.5112128164721</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.58095796120263</v>
+        <v>22.71273313774996</v>
       </c>
       <c r="C3" t="n">
-        <v>34.93549205562275</v>
+        <v>30.74342935848887</v>
       </c>
       <c r="D3" t="n">
-        <v>78.18638716621598</v>
+        <v>70.12623851434967</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.57801271808989</v>
+        <v>22.93460811890974</v>
       </c>
       <c r="C4" t="n">
-        <v>96.94562229896403</v>
+        <v>58.84890263566655</v>
       </c>
       <c r="D4" t="n">
-        <v>95.65658756328797</v>
+        <v>93.23167073379835</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.19441140763665</v>
+        <v>31.07231483941155</v>
       </c>
       <c r="C5" t="n">
-        <v>106.8386939146592</v>
+        <v>70.83309686140738</v>
       </c>
       <c r="D5" t="n">
-        <v>55.64055113818799</v>
+        <v>60.77018289287758</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.1635763181775</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C6" t="n">
-        <v>128.7247954854333</v>
+        <v>98.93857013858508</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>31.07427833482005</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>121.5099316069235</v>
+        <v>90.06946137841938</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>29.22466566001905</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>59.58226817073891</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>50.58749570442963</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
         <v>28.32833000604172</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.654064955206628</v>
+        <v>4.155738032076748</v>
       </c>
       <c r="C2" t="n">
-        <v>4.646611884200153</v>
+        <v>1.817215000560846</v>
       </c>
       <c r="D2" t="n">
-        <v>10.36823750455056</v>
+        <v>10.97004884725386</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.49398332615217</v>
+        <v>23.95464398362218</v>
       </c>
       <c r="C3" t="n">
-        <v>34.53297549688155</v>
+        <v>22.13841073076557</v>
       </c>
       <c r="D3" t="n">
-        <v>72.96839811814418</v>
+        <v>66.32196616039327</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.24840753137022</v>
+        <v>32.67256359733385</v>
       </c>
       <c r="C4" t="n">
-        <v>94.90358707413067</v>
+        <v>70.39916437613027</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1122416712455</v>
+        <v>106.7218659378538</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.86967390170921</v>
+        <v>34.63115026730624</v>
       </c>
       <c r="C5" t="n">
-        <v>142.5988540418492</v>
+        <v>91.4497986505904</v>
       </c>
       <c r="D5" t="n">
-        <v>71.02944640225674</v>
+        <v>76.0118160013093</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>152.6342790746601</v>
+        <v>111.3360801478138</v>
       </c>
       <c r="D6" t="n">
-        <v>36.50825187782615</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>149.4769784578023</v>
+        <v>113.8444455321644</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>113.0727918366264</v>
+        <v>80.77820110542756</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>55.91249525226433</v>
+        <v>43.82030877905637</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.991385254840031</v>
+        <v>4.580834788015617</v>
       </c>
       <c r="C2" t="n">
-        <v>10.58127675637212</v>
+        <v>5.867906028283186</v>
       </c>
       <c r="D2" t="n">
-        <v>13.44798005277281</v>
+        <v>19.04492371468387</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.40991287648544</v>
+        <v>18.8691908756237</v>
       </c>
       <c r="C3" t="n">
-        <v>25.90832191507333</v>
+        <v>13.63156687346696</v>
       </c>
       <c r="D3" t="n">
-        <v>65.60529033629311</v>
+        <v>60.54438092090079</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.22136056400782</v>
+        <v>40.02389040673396</v>
       </c>
       <c r="C4" t="n">
-        <v>90.42387229965247</v>
+        <v>62.15444715586556</v>
       </c>
       <c r="D4" t="n">
-        <v>120.5566545860998</v>
+        <v>113.8051756239945</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.07293673421731</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="C5" t="n">
-        <v>158.4049920802229</v>
+        <v>112.7782675253524</v>
       </c>
       <c r="D5" t="n">
-        <v>90.76257525761763</v>
+        <v>96.01492547533807</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.34095385747668</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="C6" t="n">
-        <v>189.2632859201086</v>
+        <v>129.8115901940345</v>
       </c>
       <c r="D6" t="n">
-        <v>47.53720558733482</v>
+        <v>52.28690098048088</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.75124228239384</v>
+        <v>29.8235317596096</v>
       </c>
       <c r="C7" t="n">
-        <v>184.3309854539726</v>
+        <v>137.6194296859094</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>152.3770611761474</v>
+        <v>115.8265941470387</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>91.52342972840887</v>
+        <v>70.77811898996953</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.785799074024948</v>
+        <v>2.636974333606933</v>
       </c>
       <c r="C2" t="n">
-        <v>4.962734644967626</v>
+        <v>2.549598787928967</v>
       </c>
       <c r="D2" t="n">
-        <v>9.414960483726912</v>
+        <v>12.97870465014283</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.49197877301467</v>
+        <v>19.20298509506761</v>
       </c>
       <c r="C3" t="n">
-        <v>34.18936380039517</v>
+        <v>18.90846078379357</v>
       </c>
       <c r="D3" t="n">
-        <v>64.30447462816608</v>
+        <v>63.15582981419731</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.75663404700058</v>
+        <v>44.63123238276425</v>
       </c>
       <c r="C4" t="n">
-        <v>89.68363453065037</v>
+        <v>57.07488453409257</v>
       </c>
       <c r="D4" t="n">
-        <v>127.4485234699124</v>
+        <v>120.4035019442373</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.06097583531709</v>
+        <v>44.64497685062371</v>
       </c>
       <c r="C5" t="n">
-        <v>185.3048791765855</v>
+        <v>129.885221271853</v>
       </c>
       <c r="D5" t="n">
-        <v>96.03946916794425</v>
+        <v>105.7833151325938</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.3497485290859</v>
+        <v>36.6290068454485</v>
       </c>
       <c r="C6" t="n">
-        <v>229.9979616647173</v>
+        <v>166.9236169099725</v>
       </c>
       <c r="D6" t="n">
-        <v>46.97368240509714</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>196.7275137154971</v>
+        <v>148.6984525283346</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>113.7403802755142</v>
+        <v>91.87685890193774</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.052834449580081</v>
+        <v>4.108614142272901</v>
       </c>
       <c r="C2" t="n">
-        <v>4.516039439535327</v>
+        <v>6.363688618927824</v>
       </c>
       <c r="D2" t="n">
-        <v>10.67257929286708</v>
+        <v>15.79435706592268</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.84340339340602</v>
+        <v>13.96536109291088</v>
       </c>
       <c r="C3" t="n">
-        <v>26.53173170727005</v>
+        <v>14.03408343220816</v>
       </c>
       <c r="D3" t="n">
-        <v>57.63840771633024</v>
+        <v>59.05703314896688</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.75739481052658</v>
+        <v>41.47884050442774</v>
       </c>
       <c r="C4" t="n">
-        <v>88.29249803373266</v>
+        <v>51.85493199061228</v>
       </c>
       <c r="D4" t="n">
-        <v>130.052118381575</v>
+        <v>124.3088943117311</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.96404485450392</v>
+        <v>55.32148313430778</v>
       </c>
       <c r="C5" t="n">
-        <v>177.4263538500048</v>
+        <v>118.5705789804085</v>
       </c>
       <c r="D5" t="n">
-        <v>116.9261515757951</v>
+        <v>124.0929098167969</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.44033135978387</v>
+        <v>47.33594730796422</v>
       </c>
       <c r="C6" t="n">
-        <v>261.313749934782</v>
+        <v>189.7463057905981</v>
       </c>
       <c r="D6" t="n">
-        <v>61.18251692866124</v>
+        <v>68.38756333012859</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C7" t="n">
-        <v>258.9497014629557</v>
+        <v>193.0145438980357</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>174.0736854400019</v>
+        <v>140.8611606053323</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>64.6765570080756</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>22.34752299177014</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.495201753567892</v>
+        <v>2.686061718819273</v>
       </c>
       <c r="C2" t="n">
-        <v>3.442989198793564</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="D2" t="n">
-        <v>7.972773106188347</v>
+        <v>11.42263453891164</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.336420667387166</v>
+        <v>14.25988540418492</v>
       </c>
       <c r="C3" t="n">
-        <v>22.64401079845268</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="D3" t="n">
-        <v>53.9863062565321</v>
+        <v>58.29617867817561</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.34149363682442</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="C4" t="n">
-        <v>81.01774754526377</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D4" t="n">
-        <v>130.0010675009542</v>
+        <v>125.9297597714426</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.866491978885</v>
+        <v>60.59837704463438</v>
       </c>
       <c r="C5" t="n">
-        <v>177.745421853885</v>
+        <v>113.0482481440202</v>
       </c>
       <c r="D5" t="n">
-        <v>130.9406000539184</v>
+        <v>137.0274358202486</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.88059629964295</v>
+        <v>56.07055663264809</v>
       </c>
       <c r="C6" t="n">
-        <v>281.4395778718417</v>
+        <v>199.2054449210161</v>
       </c>
       <c r="D6" t="n">
-        <v>72.89574878802993</v>
+        <v>81.8316163920844</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>308.4160412891355</v>
+        <v>231.5216341017083</v>
       </c>
       <c r="D7" t="n">
-        <v>43.17824578047897</v>
+        <v>46.77144237802229</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>220.8048761621501</v>
+        <v>180.1654299448534</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>86.97499261463339</v>
+        <v>81.7609305573786</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.307107104980004</v>
+        <v>5.144357970253286</v>
       </c>
       <c r="C2" t="n">
-        <v>9.371763584740052</v>
+        <v>7.033240553224149</v>
       </c>
       <c r="D2" t="n">
-        <v>7.702792487520473</v>
+        <v>10.13065456012284</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.299294181075036</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C3" t="n">
-        <v>18.36849954645782</v>
+        <v>17.57819264453914</v>
       </c>
       <c r="D3" t="n">
-        <v>48.83213080923635</v>
+        <v>54.77661315845079</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.94286301117121</v>
+        <v>31.9961394291078</v>
       </c>
       <c r="C4" t="n">
-        <v>69.19946868154068</v>
+        <v>47.04338649209866</v>
       </c>
       <c r="D4" t="n">
-        <v>127.5378625109989</v>
+        <v>124.8194031179395</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.49204519293946</v>
+        <v>59.17484287347651</v>
       </c>
       <c r="C5" t="n">
-        <v>164.9827016986765</v>
+        <v>100.0891784479623</v>
       </c>
       <c r="D5" t="n">
-        <v>142.9424657383356</v>
+        <v>149.0047578120597</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.36740429222912</v>
+        <v>66.41523219229674</v>
       </c>
       <c r="C6" t="n">
-        <v>285.7062533944983</v>
+        <v>191.5173786490593</v>
       </c>
       <c r="D6" t="n">
-        <v>88.91590782592939</v>
+        <v>101.3134178351581</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.16477905005999</v>
+        <v>40.00425545264903</v>
       </c>
       <c r="C7" t="n">
-        <v>349.3185958911703</v>
+        <v>258.1112889235289</v>
       </c>
       <c r="D7" t="n">
-        <v>51.02339168511523</v>
+        <v>56.53295980134833</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>294.4065015495335</v>
+        <v>237.6614842440679</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>156.5327992082241</v>
+        <v>139.6703006400809</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>57.36842709766236</v>
+        <v>57.93784076612553</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>25.23287949455151</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>30.58536797810513</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.821763886183585</v>
+        <v>5.234678759043994</v>
       </c>
       <c r="C2" t="n">
-        <v>11.21254053020282</v>
+        <v>4.177336481570178</v>
       </c>
       <c r="D2" t="n">
-        <v>11.65629049252238</v>
+        <v>8.096473316923445</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.650317890838888</v>
+        <v>3.516620276612075</v>
       </c>
       <c r="C2" t="n">
-        <v>5.323036052426207</v>
+        <v>3.768929436603505</v>
       </c>
       <c r="D2" t="n">
-        <v>5.668611244321084</v>
+        <v>7.37488875430204</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.13654504634832</v>
+        <v>16.62589737141974</v>
       </c>
       <c r="C3" t="n">
-        <v>26.56118413839745</v>
+        <v>23.62575850269949</v>
       </c>
       <c r="D3" t="n">
-        <v>52.63640316319274</v>
+        <v>58.99321954819084</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.98261594542659</v>
+        <v>44.7078087036955</v>
       </c>
       <c r="C4" t="n">
-        <v>97.82624998967341</v>
+        <v>65.72800879932396</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6985092815969</v>
+        <v>129.7330503776948</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.80233422074368</v>
+        <v>40.6934423410303</v>
       </c>
       <c r="C5" t="n">
-        <v>244.2588288166065</v>
+        <v>156.1469723604552</v>
       </c>
       <c r="D5" t="n">
-        <v>129.4679784975481</v>
+        <v>139.8008730847458</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.07299348747954</v>
+        <v>24.83527167433157</v>
       </c>
       <c r="C6" t="n">
-        <v>286.0685182973654</v>
+        <v>215.024345679545</v>
       </c>
       <c r="D6" t="n">
-        <v>72.77499382040757</v>
+        <v>82.63664950956678</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>207.0280106284546</v>
+        <v>167.1435283957237</v>
       </c>
       <c r="D7" t="n">
-        <v>32.15910954801276</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>115.3259028178728</v>
+        <v>102.892068143587</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>26.28629478120835</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>44.15312125079604</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.446155426084557</v>
+        <v>6.137886646951058</v>
       </c>
       <c r="C2" t="n">
-        <v>7.149086782325274</v>
+        <v>3.013965452037707</v>
       </c>
       <c r="D2" t="n">
-        <v>11.62094757516949</v>
+        <v>13.57855249743763</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.36511233498858</v>
+        <v>11.12320148911636</v>
       </c>
       <c r="C3" t="n">
-        <v>28.2546989282232</v>
+        <v>10.69123249924777</v>
       </c>
       <c r="D3" t="n">
-        <v>12.92470852640926</v>
+        <v>9.935286766977722</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39707765108028</v>
+        <v>13.39899732350149</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13764182036144</v>
+        <v>70.14769187009603</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576126782480032</v>
+        <v>1.576352626294293</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.85041449605599</v>
+        <v>4.126285600949344</v>
       </c>
       <c r="C2" t="n">
-        <v>5.595961914206819</v>
+        <v>8.992808970900782</v>
       </c>
       <c r="D2" t="n">
-        <v>13.62567638724148</v>
+        <v>18.57957530287089</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.30959468420301</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01907947920397</v>
+        <v>11.3735471536993</v>
       </c>
       <c r="D3" t="n">
-        <v>19.5613230071177</v>
+        <v>18.93791321492097</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.39634833507523</v>
+        <v>12.99244911800229</v>
       </c>
       <c r="C4" t="n">
-        <v>43.59745205019236</v>
+        <v>17.10204500797943</v>
       </c>
       <c r="D4" t="n">
-        <v>21.8370141855618</v>
+        <v>20.27996232662636</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43822450806219</v>
+        <v>15.44498694682498</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12904199234694</v>
+        <v>86.16676928228672</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250152528013092</v>
+        <v>3.251576199331574</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.3245986372072</v>
+        <v>4.941136195474197</v>
       </c>
       <c r="C2" t="n">
-        <v>6.960591223109885</v>
+        <v>6.892850631516856</v>
       </c>
       <c r="D2" t="n">
-        <v>13.21628759457056</v>
+        <v>17.74214451114836</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50179625005713</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23444207933251</v>
+        <v>25.69724615866026</v>
       </c>
       <c r="D3" t="n">
-        <v>25.92304813063703</v>
+        <v>29.40334374219197</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.36777984066083</v>
+        <v>24.3767954964483</v>
       </c>
       <c r="C4" t="n">
-        <v>59.25730968063323</v>
+        <v>23.63655772744621</v>
       </c>
       <c r="D4" t="n">
-        <v>26.73789872516188</v>
+        <v>25.21913502669207</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.61545799957152</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>48.25289966373074</v>
+        <v>20.59215809657685</v>
       </c>
       <c r="D5" t="n">
-        <v>30.50780990946964</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72905551818743</v>
+        <v>16.74373142997131</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0472386609433</v>
+        <v>102.136761722825</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182263879546857</v>
+        <v>5.023119428991394</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.590652265058085</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="C2" t="n">
-        <v>6.758351196035043</v>
+        <v>4.229369109895258</v>
       </c>
       <c r="D2" t="n">
-        <v>17.62924352515997</v>
+        <v>20.27112659728814</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.26126806251667</v>
+        <v>16.38046044535803</v>
       </c>
       <c r="C3" t="n">
-        <v>25.82487336021235</v>
+        <v>26.32065595085699</v>
       </c>
       <c r="D3" t="n">
-        <v>30.19855938263188</v>
+        <v>36.34430001121692</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.14179794223482</v>
+        <v>27.56747553525043</v>
       </c>
       <c r="C4" t="n">
-        <v>60.03583561010095</v>
+        <v>46.76260664868407</v>
       </c>
       <c r="D4" t="n">
-        <v>33.3362250454047</v>
+        <v>33.55319128804324</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.96722677732814</v>
+        <v>24.42097414313941</v>
       </c>
       <c r="C5" t="n">
-        <v>81.28870991163591</v>
+        <v>33.28124717396688</v>
       </c>
       <c r="D5" t="n">
-        <v>32.88854809226815</v>
+        <v>32.25041208450773</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.59247689174634</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>45.36361617013237</v>
+        <v>22.90319219237384</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05148078474255</v>
+        <v>18.07807326911151</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7644222623681</v>
+        <v>117.9379065651561</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017160261580849</v>
+        <v>6.886885054899623</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.177737392197677</v>
+        <v>5.759913780816037</v>
       </c>
       <c r="C2" t="n">
-        <v>11.39907259400971</v>
+        <v>3.046363126277853</v>
       </c>
       <c r="D2" t="n">
-        <v>29.54766065471625</v>
+        <v>18.87508136184918</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.81319019875262</v>
+        <v>15.13364086096458</v>
       </c>
       <c r="C3" t="n">
-        <v>24.48969648243668</v>
+        <v>19.33552103514093</v>
       </c>
       <c r="D3" t="n">
-        <v>34.69496386808228</v>
+        <v>41.08123268420778</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.07125097624929</v>
+        <v>21.76043786463055</v>
       </c>
       <c r="C4" t="n">
-        <v>52.37820351697583</v>
+        <v>48.31965850761951</v>
       </c>
       <c r="D4" t="n">
-        <v>35.35273482992764</v>
+        <v>37.79041437957247</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.78850763742621</v>
+        <v>20.49398332615217</v>
       </c>
       <c r="C5" t="n">
-        <v>72.20754364735292</v>
+        <v>46.09305471438775</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>30.11511082777092</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.71952325622168</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>59.49194738194822</v>
+        <v>26.40508625342222</v>
       </c>
       <c r="D6" t="n">
-        <v>31.19503330244241</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>27.90716024091983</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>34.29539255245382</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053763038088216</v>
+        <v>7.069541575435528</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12902848207702</v>
+        <v>67.16064496663751</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408601898805135</v>
+        <v>5.302156181576645</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.042837046088365</v>
+        <v>5.075635630956009</v>
       </c>
       <c r="C2" t="n">
-        <v>5.521349088684061</v>
+        <v>4.126285600949344</v>
       </c>
       <c r="D2" t="n">
-        <v>31.03991716517141</v>
+        <v>19.73803759388212</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6209886328985</v>
+        <v>18.36849954645782</v>
       </c>
       <c r="C3" t="n">
-        <v>37.42422248588841</v>
+        <v>14.41696503686441</v>
       </c>
       <c r="D3" t="n">
-        <v>51.12942043717388</v>
+        <v>47.36932672990861</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.69586350032851</v>
+        <v>26.99315312826605</v>
       </c>
       <c r="C4" t="n">
-        <v>58.10866486666446</v>
+        <v>48.52386203010285</v>
       </c>
       <c r="D4" t="n">
-        <v>44.98858854711009</v>
+        <v>51.21679598285185</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.39076094848602</v>
+        <v>27.80800372279091</v>
       </c>
       <c r="C5" t="n">
-        <v>87.4000893705723</v>
+        <v>73.43472827766143</v>
       </c>
       <c r="D5" t="n">
-        <v>36.69282044622454</v>
+        <v>37.47821860962199</v>
       </c>
     </row>
     <row r="6">
@@ -6126,10 +6126,10 @@
         <v>21.53463589265379</v>
       </c>
       <c r="C6" t="n">
-        <v>92.13604029585892</v>
+        <v>54.86300695642451</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>61.74309486778615</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.274599265480937</v>
+        <v>7.298282208665436</v>
       </c>
       <c r="C21" t="n">
-        <v>75.47396737936474</v>
+        <v>77.54424846707025</v>
       </c>
       <c r="D21" t="n">
-        <v>5.455949449110703</v>
+        <v>6.385996932582256</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.698243601897735</v>
+        <v>4.031056073637403</v>
       </c>
       <c r="C2" t="n">
-        <v>6.669012154948583</v>
+        <v>3.401755795215198</v>
       </c>
       <c r="D2" t="n">
-        <v>28.00435326364027</v>
+        <v>23.0533995911236</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.14345833800705</v>
+        <v>18.0199791114502</v>
       </c>
       <c r="C3" t="n">
-        <v>27.89636101617312</v>
+        <v>15.46252634188726</v>
       </c>
       <c r="D3" t="n">
-        <v>64.09830761027426</v>
+        <v>52.50386722311941</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.18834099496192</v>
+        <v>32.46836007485052</v>
       </c>
       <c r="C4" t="n">
-        <v>78.15889823049707</v>
+        <v>41.04490801915065</v>
       </c>
       <c r="D4" t="n">
-        <v>60.49529353568845</v>
+        <v>64.15819422023331</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.66765485881262</v>
+        <v>35.02384934900497</v>
       </c>
       <c r="C5" t="n">
-        <v>98.88653751026</v>
+        <v>83.15403054970486</v>
       </c>
       <c r="D5" t="n">
-        <v>44.30136515413732</v>
+        <v>48.03200643027521</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.22899356146354</v>
+        <v>30.95352336719769</v>
       </c>
       <c r="C6" t="n">
-        <v>118.0983583346658</v>
+        <v>89.51968266404117</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>100.7891645610903</v>
+        <v>58.32955810011999</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>57.24570863463151</v>
+        <v>32.3780392860598</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.48192327383124</v>
+        <v>7.516644626486083</v>
       </c>
       <c r="C21" t="n">
-        <v>84.17163683060144</v>
+        <v>87.3809937829007</v>
       </c>
       <c r="D21" t="n">
-        <v>6.546682864602334</v>
+        <v>7.516644626486083</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_68_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497613040416</v>
+        <v>10.84497644362976</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907123870403</v>
+        <v>37.78907233013149</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.371722527011046</v>
+        <v>0.8393942871310229</v>
       </c>
       <c r="C2" t="n">
-        <v>4.895975801078843</v>
+        <v>2.432770811123596</v>
       </c>
       <c r="D2" t="n">
-        <v>22.70487915611599</v>
+        <v>15.75214191464007</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.87486037767093</v>
+        <v>7.127488332831844</v>
       </c>
       <c r="C3" t="n">
-        <v>14.13716694115407</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D3" t="n">
-        <v>58.34526606338795</v>
+        <v>81.37215846649688</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.69358120975053</v>
+        <v>13.3115171218825</v>
       </c>
       <c r="C4" t="n">
-        <v>39.71758512300897</v>
+        <v>100.3532685804047</v>
       </c>
       <c r="D4" t="n">
-        <v>74.7767773893668</v>
+        <v>98.86003032224532</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.58330667170541</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C5" t="n">
-        <v>78.39255418410782</v>
+        <v>104.9979169691964</v>
       </c>
       <c r="D5" t="n">
-        <v>60.30385273336034</v>
+        <v>59.51845456996289</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.64788103600744</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>112.7851397592821</v>
+        <v>60.53849043467533</v>
       </c>
       <c r="D6" t="n">
-        <v>44.1560664939088</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.56591295046944</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>96.41744203407924</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>56.24432597629976</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.65583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>18.41660518396592</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.723035795686934</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.53794744608668</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.6884152701478</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.10687163104266</v>
+        <v>1.233075116533994</v>
       </c>
       <c r="C2" t="n">
-        <v>6.90070461315083</v>
+        <v>5.943500601510189</v>
       </c>
       <c r="D2" t="n">
-        <v>19.93536888243573</v>
+        <v>19.32963054891545</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2661768010379</v>
+        <v>4.889103567149116</v>
       </c>
       <c r="C3" t="n">
-        <v>16.75352457297182</v>
+        <v>18.66302385773187</v>
       </c>
       <c r="D3" t="n">
-        <v>62.27225688037518</v>
+        <v>75.24605279199679</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.83022406709009</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C4" t="n">
-        <v>37.3820073346058</v>
+        <v>88.22868443295661</v>
       </c>
       <c r="D4" t="n">
-        <v>85.79100488331179</v>
+        <v>116.408770535657</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.95208395560371</v>
+        <v>17.22967220953153</v>
       </c>
       <c r="C5" t="n">
-        <v>75.00552460445633</v>
+        <v>150.2564861349744</v>
       </c>
       <c r="D5" t="n">
-        <v>71.49577656177398</v>
+        <v>80.25787482217676</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.42274201656544</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>119.1851530432671</v>
+        <v>116.2065305085822</v>
       </c>
       <c r="D6" t="n">
-        <v>52.48815925985148</v>
+        <v>41.57996051796516</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.84833749412304</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>128.9957578518054</v>
+        <v>61.50354842794993</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.28214680621311</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>92.12720456652069</v>
+        <v>37.38495257771854</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53749902030851</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>51.80780810080841</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.19226798577891</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.916685815547335</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8856727829456</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.895857269434169</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.63308840051895</v>
+        <v>0.6577709618453629</v>
       </c>
       <c r="C2" t="n">
-        <v>5.592034923389832</v>
+        <v>2.468113728476481</v>
       </c>
       <c r="D2" t="n">
-        <v>17.86388122647496</v>
+        <v>13.02190154912969</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32570355809846</v>
+        <v>5.046183199828605</v>
       </c>
       <c r="C3" t="n">
-        <v>21.72607669498191</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D3" t="n">
-        <v>63.17055602976101</v>
+        <v>75.93818492349078</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.13278228644735</v>
+        <v>14.98343346221482</v>
       </c>
       <c r="C4" t="n">
-        <v>39.14326271602458</v>
+        <v>80.07330625377834</v>
       </c>
       <c r="D4" t="n">
-        <v>95.59277396251193</v>
+        <v>128.6992700451229</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.73748211900116</v>
+        <v>17.67145867644259</v>
       </c>
       <c r="C5" t="n">
-        <v>71.98665041389738</v>
+        <v>172.542159021377</v>
       </c>
       <c r="D5" t="n">
-        <v>82.98222470146166</v>
+        <v>90.02626447943253</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.18502020341747</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>118.5411265492811</v>
+        <v>153.1978022568978</v>
       </c>
       <c r="D6" t="n">
-        <v>61.70578845502478</v>
+        <v>41.861722109084</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.01098881785852</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>150.2555043872701</v>
+        <v>60.78490910844126</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.71045084717197</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>128.0935317116026</v>
+        <v>38.63668090063322</v>
       </c>
       <c r="D8" t="n">
-        <v>41.55738032076748</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>80.87343063273947</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>37.43894870145212</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45032876327558</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.097085629343317</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.3713345144744</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.13349274034706</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.840818003191774</v>
+        <v>0.7098035901704439</v>
       </c>
       <c r="C2" t="n">
-        <v>3.623630776374977</v>
+        <v>4.287292224445821</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5112128164721</v>
+        <v>11.90369091399258</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.71273313774996</v>
+        <v>3.617740290149497</v>
       </c>
       <c r="C3" t="n">
-        <v>30.74342935848887</v>
+        <v>15.12382338392211</v>
       </c>
       <c r="D3" t="n">
-        <v>70.12623851434967</v>
+        <v>69.67463457039614</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.93460811890974</v>
+        <v>12.57127935288041</v>
       </c>
       <c r="C4" t="n">
-        <v>58.84890263566655</v>
+        <v>67.38716241950105</v>
       </c>
       <c r="D4" t="n">
-        <v>93.23167073379835</v>
+        <v>136.663207421973</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.07231483941155</v>
+        <v>20.24854640009047</v>
       </c>
       <c r="C5" t="n">
-        <v>70.83309686140738</v>
+        <v>161.3256915003572</v>
       </c>
       <c r="D5" t="n">
-        <v>60.77018289287758</v>
+        <v>112.9746170662017</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.18245050873644</v>
+        <v>17.30821202587127</v>
       </c>
       <c r="C6" t="n">
-        <v>98.93857013858508</v>
+        <v>215.6683721735308</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>57.92213280285758</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>90.06946137841938</v>
+        <v>135.6431715572606</v>
       </c>
       <c r="D7" t="n">
-        <v>29.22466566001905</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>59.58226817073891</v>
+        <v>57.82984851865836</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.155738032076748</v>
+        <v>0.476147636559703</v>
       </c>
       <c r="C2" t="n">
-        <v>1.817215000560846</v>
+        <v>2.145118733779281</v>
       </c>
       <c r="D2" t="n">
-        <v>10.97004884725386</v>
+        <v>8.606982123131786</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.95464398362218</v>
+        <v>3.136683915068559</v>
       </c>
       <c r="C3" t="n">
-        <v>22.13841073076557</v>
+        <v>16.14974973486003</v>
       </c>
       <c r="D3" t="n">
-        <v>66.32196616039327</v>
+        <v>64.27993093555992</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.67256359733385</v>
+        <v>10.51648140789183</v>
       </c>
       <c r="C4" t="n">
-        <v>70.39916437613027</v>
+        <v>54.71378130537899</v>
       </c>
       <c r="D4" t="n">
-        <v>106.7218659378538</v>
+        <v>140.6451761103981</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.63115026730624</v>
+        <v>21.10757564130643</v>
       </c>
       <c r="C5" t="n">
-        <v>91.4497986505904</v>
+        <v>150.7473599870978</v>
       </c>
       <c r="D5" t="n">
-        <v>76.0118160013093</v>
+        <v>131.8241729877405</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>20.89060939866788</v>
       </c>
       <c r="C6" t="n">
-        <v>111.3360801478138</v>
+        <v>244.4483061235261</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>72.33222560579226</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>113.8444455321644</v>
+        <v>199.3026379437365</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>41.44153409166636</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>80.77820110542756</v>
+        <v>90.45823346930109</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>43.82030877905637</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.580834788015617</v>
+        <v>0.5173810401380691</v>
       </c>
       <c r="C2" t="n">
-        <v>5.867906028283186</v>
+        <v>4.554327600000953</v>
       </c>
       <c r="D2" t="n">
-        <v>19.04492371468387</v>
+        <v>9.449321653375549</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8691908756237</v>
+        <v>2.375829444277281</v>
       </c>
       <c r="C3" t="n">
-        <v>13.63156687346696</v>
+        <v>11.97241325328985</v>
       </c>
       <c r="D3" t="n">
-        <v>60.54438092090079</v>
+        <v>57.06899404786709</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.02389040673396</v>
+        <v>8.308530821040756</v>
       </c>
       <c r="C4" t="n">
-        <v>62.15444715586556</v>
+        <v>47.86020058203201</v>
       </c>
       <c r="D4" t="n">
-        <v>113.8051756239945</v>
+        <v>140.6834642708637</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.99425804915732</v>
+        <v>19.19316761802515</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7782675253524</v>
+        <v>126.6209101552324</v>
       </c>
       <c r="D5" t="n">
-        <v>96.01492547533807</v>
+        <v>149.1029325824844</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>24.43275511559037</v>
       </c>
       <c r="C6" t="n">
-        <v>129.8115901940345</v>
+        <v>243.3212597590507</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28690098048088</v>
+        <v>92.05553698411069</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.8235317596096</v>
+        <v>15.39085875947725</v>
       </c>
       <c r="C7" t="n">
-        <v>137.6194296859094</v>
+        <v>272.0049824340298</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>50.06520592577034</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>115.8265941470387</v>
+        <v>166.4798669476529</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>42.14152020479433</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>74.32811868852599</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.29272504678157</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.636974333606933</v>
+        <v>0.3475386873033709</v>
       </c>
       <c r="C2" t="n">
-        <v>2.549598787928967</v>
+        <v>2.367975462643307</v>
       </c>
       <c r="D2" t="n">
-        <v>12.97870465014283</v>
+        <v>6.804493338134643</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.20298509506761</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90846078379357</v>
+        <v>15.9141302858408</v>
       </c>
       <c r="D3" t="n">
-        <v>63.15582981419731</v>
+        <v>61.16288197457629</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.63123238276425</v>
+        <v>13.28599168157209</v>
       </c>
       <c r="C4" t="n">
-        <v>57.07488453409257</v>
+        <v>67.45097602027711</v>
       </c>
       <c r="D4" t="n">
-        <v>120.4035019442373</v>
+        <v>145.4184334484461</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.64497685062371</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="C5" t="n">
-        <v>129.885221271853</v>
+        <v>197.5276380944583</v>
       </c>
       <c r="D5" t="n">
-        <v>105.7833151325938</v>
+        <v>136.6101930459437</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.6290068454485</v>
+        <v>9.539642442166258</v>
       </c>
       <c r="C6" t="n">
-        <v>166.9236169099725</v>
+        <v>241.1476703418483</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>74.90833158173589</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>148.6984525283346</v>
+        <v>117.0783224699534</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>91.87685890193774</v>
+        <v>54.74225198880214</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.108614142272901</v>
+        <v>0.1767145867644259</v>
       </c>
       <c r="C2" t="n">
-        <v>6.363688618927824</v>
+        <v>1.525635932399543</v>
       </c>
       <c r="D2" t="n">
-        <v>15.79435706592268</v>
+        <v>5.21700730036755</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.96536109291088</v>
+        <v>2.194206118991621</v>
       </c>
       <c r="C3" t="n">
-        <v>14.03408343220816</v>
+        <v>12.25221134900019</v>
       </c>
       <c r="D3" t="n">
-        <v>59.05703314896688</v>
+        <v>52.86711387369073</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.47884050442774</v>
+        <v>9.150870351284519</v>
       </c>
       <c r="C4" t="n">
-        <v>51.85493199061228</v>
+        <v>50.74457533710914</v>
       </c>
       <c r="D4" t="n">
-        <v>124.3088943117311</v>
+        <v>137.5310723925272</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.32148313430778</v>
+        <v>14.01444847812322</v>
       </c>
       <c r="C5" t="n">
-        <v>118.5705789804085</v>
+        <v>146.6485633218673</v>
       </c>
       <c r="D5" t="n">
-        <v>124.0929098167969</v>
+        <v>140.3653780146877</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.33594730796422</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>189.7463057905981</v>
+        <v>229.9577100088432</v>
       </c>
       <c r="D6" t="n">
-        <v>68.38756333012859</v>
+        <v>82.39513957432206</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C7" t="n">
-        <v>193.0145438980357</v>
+        <v>158.0407636819473</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.67588438887831</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>140.8611606053323</v>
+        <v>62.83676181031709</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>64.6765570080756</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>18.50594422505238</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.686061718819273</v>
+        <v>0.3858268477689965</v>
       </c>
       <c r="C2" t="n">
-        <v>4.07228947721577</v>
+        <v>12.53986342634451</v>
       </c>
       <c r="D2" t="n">
-        <v>11.42263453891164</v>
+        <v>14.47783339452771</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.25988540418492</v>
+        <v>1.315541923690726</v>
       </c>
       <c r="C3" t="n">
-        <v>19.61041039233004</v>
+        <v>8.418486563916399</v>
       </c>
       <c r="D3" t="n">
-        <v>58.29617867817561</v>
+        <v>44.77260405217579</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.66729500591412</v>
+        <v>6.53451271946677</v>
       </c>
       <c r="C4" t="n">
-        <v>45.33318199130072</v>
+        <v>39.47509344006</v>
       </c>
       <c r="D4" t="n">
-        <v>125.9297597714426</v>
+        <v>133.3321374614636</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.59837704463438</v>
+        <v>14.25988540418492</v>
       </c>
       <c r="C5" t="n">
-        <v>113.0482481440202</v>
+        <v>117.2206758870692</v>
       </c>
       <c r="D5" t="n">
-        <v>137.0274358202486</v>
+        <v>158.7240600841031</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.07055663264809</v>
+        <v>14.20883452356409</v>
       </c>
       <c r="C6" t="n">
-        <v>199.2054449210161</v>
+        <v>235.0696703048563</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8316163920844</v>
+        <v>106.7876430340383</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>231.5216341017083</v>
+        <v>249.9667099690974</v>
       </c>
       <c r="D7" t="n">
-        <v>46.77144237802229</v>
+        <v>50.36463897556562</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>180.1654299448534</v>
+        <v>138.9418438435298</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>81.7609305573786</v>
+        <v>54.58124536530566</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.144357970253286</v>
+        <v>0.6528622233241289</v>
       </c>
       <c r="C2" t="n">
-        <v>7.033240553224149</v>
+        <v>9.787042863636453</v>
       </c>
       <c r="D2" t="n">
-        <v>10.13065456012284</v>
+        <v>17.21690948937631</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.70734137314322</v>
+        <v>1.310633185169492</v>
       </c>
       <c r="C3" t="n">
-        <v>17.57819264453914</v>
+        <v>30.80233422074368</v>
       </c>
       <c r="D3" t="n">
-        <v>54.77661315845079</v>
+        <v>45.66599446304039</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.9961394291078</v>
+        <v>4.479714774478196</v>
       </c>
       <c r="C4" t="n">
-        <v>47.04338649209866</v>
+        <v>29.53293443915255</v>
       </c>
       <c r="D4" t="n">
-        <v>124.8194031179395</v>
+        <v>125.0618948008884</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.17484287347651</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="C5" t="n">
-        <v>100.0891784479623</v>
+        <v>94.14960483726912</v>
       </c>
       <c r="D5" t="n">
-        <v>149.0047578120597</v>
+        <v>170.7750131537327</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.41523219229674</v>
+        <v>16.86544381125596</v>
       </c>
       <c r="C6" t="n">
-        <v>191.5173786490593</v>
+        <v>212.0457231448601</v>
       </c>
       <c r="D6" t="n">
-        <v>101.3134178351581</v>
+        <v>130.3751133762722</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.00425545264903</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>258.1112889235289</v>
+        <v>296.7980389570787</v>
       </c>
       <c r="D7" t="n">
-        <v>56.53295980134833</v>
+        <v>66.35436383463342</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>237.6614842440679</v>
+        <v>233.238710836436</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>139.6703006400809</v>
+        <v>110.0499906552504</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>57.93784076612553</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>25.23287949455151</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>17.43093048890212</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.234678759043994</v>
+        <v>3.716896808278424</v>
       </c>
       <c r="C2" t="n">
-        <v>4.177336481570178</v>
+        <v>6.44517367838031</v>
       </c>
       <c r="D2" t="n">
-        <v>8.096473316923445</v>
+        <v>24.25800402423444</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.516620276612075</v>
+        <v>0.594939108773567</v>
       </c>
       <c r="C2" t="n">
-        <v>3.768929436603505</v>
+        <v>9.51706224496858</v>
       </c>
       <c r="D2" t="n">
-        <v>7.37488875430204</v>
+        <v>26.17339379521997</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.62589737141974</v>
+        <v>1.727875959474386</v>
       </c>
       <c r="C3" t="n">
-        <v>23.62575850269949</v>
+        <v>34.26299487821368</v>
       </c>
       <c r="D3" t="n">
-        <v>58.99321954819084</v>
+        <v>48.09091129253001</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.7078087036955</v>
+        <v>3.509748042682347</v>
       </c>
       <c r="C4" t="n">
-        <v>65.72800879932396</v>
+        <v>52.69727152085604</v>
       </c>
       <c r="D4" t="n">
-        <v>129.7330503776948</v>
+        <v>120.2248238620644</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.6934423410303</v>
+        <v>9.940195505498956</v>
       </c>
       <c r="C5" t="n">
-        <v>156.1469723604552</v>
+        <v>74.41647598190823</v>
       </c>
       <c r="D5" t="n">
-        <v>139.8008730847458</v>
+        <v>174.6529165855076</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.83527167433157</v>
+        <v>17.06670209062656</v>
       </c>
       <c r="C6" t="n">
-        <v>215.024345679545</v>
+        <v>184.5538421828367</v>
       </c>
       <c r="D6" t="n">
-        <v>82.63664950956678</v>
+        <v>151.587736021933</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="C7" t="n">
-        <v>167.1435283957237</v>
+        <v>301.7686275836803</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>84.3802334323091</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.253110981246429</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>102.892068143587</v>
+        <v>309.0934472050657</v>
       </c>
       <c r="D8" t="n">
-        <v>26.28629478120835</v>
+        <v>43.30979997284804</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>44.15312125079604</v>
+        <v>190.3687338350905</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>81.28380117311467</v>
       </c>
       <c r="D10" t="n">
-        <v>19.78712497909446</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.94732978133594</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.71617710248143</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>14.10280577150543</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.137886646951058</v>
+        <v>3.908337610606552</v>
       </c>
       <c r="C2" t="n">
-        <v>3.013965452037707</v>
+        <v>6.714172549343935</v>
       </c>
       <c r="D2" t="n">
-        <v>13.57855249743763</v>
+        <v>29.31302295340127</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.12320148911636</v>
+        <v>5.998478472948012</v>
       </c>
       <c r="C3" t="n">
-        <v>10.69123249924777</v>
+        <v>12.72345024703866</v>
       </c>
       <c r="D3" t="n">
-        <v>9.935286766977722</v>
+        <v>19.47787445225672</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39899732350149</v>
+        <v>11.67683990023856</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14769187009603</v>
+        <v>59.94111148789126</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576352626294293</v>
+        <v>0.7784559933492371</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.126285600949344</v>
+        <v>2.426880324898115</v>
       </c>
       <c r="C2" t="n">
-        <v>8.992808970900782</v>
+        <v>8.528442306792043</v>
       </c>
       <c r="D2" t="n">
-        <v>18.57957530287089</v>
+        <v>21.54052637887927</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16094987023424</v>
+        <v>10.78940726967245</v>
       </c>
       <c r="C3" t="n">
-        <v>11.3735471536993</v>
+        <v>21.73098543350315</v>
       </c>
       <c r="D3" t="n">
-        <v>18.93791321492097</v>
+        <v>40.37928307567131</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.99244911800229</v>
+        <v>7.542767611728244</v>
       </c>
       <c r="C4" t="n">
-        <v>17.10204500797943</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D4" t="n">
-        <v>20.27996232662636</v>
+        <v>24.68310078017331</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44498694682498</v>
+        <v>13.62560016851996</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16676928228672</v>
+        <v>73.73854208846096</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251576199331574</v>
+        <v>1.60301178453176</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.941136195474197</v>
+        <v>1.61595672119025</v>
       </c>
       <c r="C2" t="n">
-        <v>6.892850631516856</v>
+        <v>5.246459731494955</v>
       </c>
       <c r="D2" t="n">
-        <v>17.74214451114836</v>
+        <v>26.41097673964769</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.70796326794897</v>
+        <v>9.459139130418018</v>
       </c>
       <c r="C3" t="n">
-        <v>25.69724615866026</v>
+        <v>29.07445826126929</v>
       </c>
       <c r="D3" t="n">
-        <v>29.40334374219197</v>
+        <v>48.71432108472673</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.3767954964483</v>
+        <v>15.63433219013046</v>
       </c>
       <c r="C4" t="n">
-        <v>23.63655772744621</v>
+        <v>41.78514578815274</v>
       </c>
       <c r="D4" t="n">
-        <v>25.21913502669207</v>
+        <v>40.11322944782042</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.73188506574938</v>
+        <v>7.338564089244909</v>
       </c>
       <c r="C5" t="n">
-        <v>20.59215809657685</v>
+        <v>25.59907138823559</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>28.86338250485623</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74373142997131</v>
+        <v>14.83438622636835</v>
       </c>
       <c r="C21" t="n">
-        <v>102.136761722825</v>
+        <v>87.35805222194698</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023119428991394</v>
+        <v>2.472397704394726</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.056000676871074</v>
+        <v>1.314560175986479</v>
       </c>
       <c r="C2" t="n">
-        <v>4.229369109895258</v>
+        <v>4.642684893383167</v>
       </c>
       <c r="D2" t="n">
-        <v>20.27112659728814</v>
+        <v>23.05830832964483</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38046044535803</v>
+        <v>7.274750488468865</v>
       </c>
       <c r="C3" t="n">
-        <v>26.32065595085699</v>
+        <v>23.82210804354885</v>
       </c>
       <c r="D3" t="n">
-        <v>36.34430001121692</v>
+        <v>58.53670686571607</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.56747553525043</v>
+        <v>17.1913840490659</v>
       </c>
       <c r="C4" t="n">
-        <v>46.76260664868407</v>
+        <v>60.06136105041136</v>
       </c>
       <c r="D4" t="n">
-        <v>33.55319128804324</v>
+        <v>55.50506995500192</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.42097414313941</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C5" t="n">
-        <v>33.28124717396688</v>
+        <v>55.02695882303374</v>
       </c>
       <c r="D5" t="n">
-        <v>32.25041208450773</v>
+        <v>36.49647090537518</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>7.406304680837938</v>
       </c>
       <c r="C6" t="n">
-        <v>22.90319219237384</v>
+        <v>26.92835777978577</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>34.29441080474959</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07807326911151</v>
+        <v>16.07502097316611</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9379065651561</v>
+        <v>101.5264482515754</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886885054899623</v>
+        <v>3.384214941719182</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.759913780816037</v>
+        <v>1.587486037767093</v>
       </c>
       <c r="C2" t="n">
-        <v>3.046363126277853</v>
+        <v>9.830239762623313</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87508136184918</v>
+        <v>33.10256909179395</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.13364086096458</v>
+        <v>5.753041546886308</v>
       </c>
       <c r="C3" t="n">
-        <v>19.33552103514093</v>
+        <v>20.45962215650353</v>
       </c>
       <c r="D3" t="n">
-        <v>41.08123268420778</v>
+        <v>63.03802008968769</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.76043786463055</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="C4" t="n">
-        <v>48.31965850761951</v>
+        <v>59.8188693674624</v>
       </c>
       <c r="D4" t="n">
-        <v>37.79041437957247</v>
+        <v>71.44570742885739</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.49398332615217</v>
+        <v>20.91122610045706</v>
       </c>
       <c r="C5" t="n">
-        <v>46.09305471438775</v>
+        <v>84.70028318389357</v>
       </c>
       <c r="D5" t="n">
-        <v>30.11511082777092</v>
+        <v>47.17297718905925</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.11574841810989</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C6" t="n">
-        <v>26.40508625342222</v>
+        <v>58.80766923208819</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>28.80545939030566</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.069541575435528</v>
+        <v>17.3426491201285</v>
       </c>
       <c r="C21" t="n">
-        <v>67.16064496663751</v>
+        <v>115.3286166488545</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302156181576645</v>
+        <v>4.335662280032124</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.075635630956009</v>
+        <v>1.771072858461246</v>
       </c>
       <c r="C2" t="n">
-        <v>4.126285600949344</v>
+        <v>8.527460559087794</v>
       </c>
       <c r="D2" t="n">
-        <v>19.73803759388212</v>
+        <v>27.46831901712151</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.36849954645782</v>
+        <v>5.537057051952011</v>
       </c>
       <c r="C3" t="n">
-        <v>14.41696503686441</v>
+        <v>30.0709321810798</v>
       </c>
       <c r="D3" t="n">
-        <v>47.36932672990861</v>
+        <v>73.45436323174634</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.99315312826605</v>
+        <v>13.32427984203771</v>
       </c>
       <c r="C4" t="n">
-        <v>48.52386203010285</v>
+        <v>55.19876467127691</v>
       </c>
       <c r="D4" t="n">
-        <v>51.21679598285185</v>
+        <v>85.24220791663781</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.80800372279091</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="C5" t="n">
-        <v>73.43472827766143</v>
+        <v>97.78207134298233</v>
       </c>
       <c r="D5" t="n">
-        <v>37.47821860962199</v>
+        <v>60.0093284220863</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.53463589265379</v>
+        <v>21.17237098978672</v>
       </c>
       <c r="C6" t="n">
-        <v>54.86300695642451</v>
+        <v>95.27566945404023</v>
       </c>
       <c r="D6" t="n">
-        <v>33.81139093426016</v>
+        <v>44.03531152628644</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>30.06307819944583</v>
+        <v>56.35329997147116</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>21.86352137357647</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.85168364786328</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.298282208665436</v>
+        <v>17.74198789948116</v>
       </c>
       <c r="C21" t="n">
-        <v>77.54424846707025</v>
+        <v>128.6294122712384</v>
       </c>
       <c r="D21" t="n">
-        <v>6.385996932582256</v>
+        <v>5.322596369844349</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.031056073637403</v>
+        <v>1.595340019401067</v>
       </c>
       <c r="C2" t="n">
-        <v>3.401755795215198</v>
+        <v>5.252350217720435</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0533995911236</v>
+        <v>21.59746774572558</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.0199791114502</v>
+        <v>8.182867114897164</v>
       </c>
       <c r="C3" t="n">
-        <v>15.46252634188726</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D3" t="n">
-        <v>52.50386722311941</v>
+        <v>81.52923809917638</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.46836007485052</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="C4" t="n">
-        <v>41.04490801915065</v>
+        <v>83.25122357242527</v>
       </c>
       <c r="D4" t="n">
-        <v>64.15819422023331</v>
+        <v>78.75874607779187</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.02384934900497</v>
+        <v>11.92823460659875</v>
       </c>
       <c r="C5" t="n">
-        <v>83.15403054970486</v>
+        <v>56.91682315370885</v>
       </c>
       <c r="D5" t="n">
-        <v>48.03200643027521</v>
+        <v>44.1541029985003</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.95352336719769</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="C6" t="n">
-        <v>89.51968266404117</v>
+        <v>37.11202671593793</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>25.84156307118455</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>58.32955810011999</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>32.3780392860598</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.96708790860789</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.516644626486083</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.3809937829007</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.516644626486083</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
